--- a/缓存数据/concat_area_csm_qz.xlsx
+++ b/缓存数据/concat_area_csm_qz.xlsx
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>578106.9599999998</v>
+        <v>605006.7800000001</v>
       </c>
       <c r="C2" t="n">
-        <v>415295.8699999999</v>
+        <v>410153.8900000001</v>
       </c>
       <c r="D2" t="n">
-        <v>385053.1699999998</v>
+        <v>387168.53</v>
       </c>
       <c r="E2" t="n">
-        <v>30242.7</v>
+        <v>22985.36</v>
       </c>
       <c r="F2" t="n">
-        <v>330456.6899999999</v>
+        <v>333478.6900000001</v>
       </c>
       <c r="G2" t="n">
-        <v>84839.17999999996</v>
+        <v>76675.19999999997</v>
       </c>
       <c r="H2" t="n">
-        <v>1803.47</v>
+        <v>1794.73</v>
       </c>
       <c r="I2" t="n">
-        <v>162811.0899999999</v>
+        <v>194852.89</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>605006.7800000003</v>
+        <v>620110.3699999998</v>
       </c>
       <c r="C3" t="n">
-        <v>410153.8900000002</v>
+        <v>402186.1999999998</v>
       </c>
       <c r="D3" t="n">
-        <v>387168.5300000001</v>
+        <v>366618.5799999998</v>
       </c>
       <c r="E3" t="n">
-        <v>22985.36</v>
+        <v>35567.62</v>
       </c>
       <c r="F3" t="n">
-        <v>333478.6900000002</v>
+        <v>319541.4199999998</v>
       </c>
       <c r="G3" t="n">
-        <v>76675.19999999995</v>
+        <v>82644.78000000004</v>
       </c>
       <c r="H3" t="n">
-        <v>1794.73</v>
+        <v>1766.88</v>
       </c>
       <c r="I3" t="n">
-        <v>194852.89</v>
+        <v>217924.17</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>620110.3700000001</v>
+        <v>627192.9400000002</v>
       </c>
       <c r="C4" t="n">
-        <v>402186.2000000001</v>
+        <v>397426.8400000003</v>
       </c>
       <c r="D4" t="n">
-        <v>366618.58</v>
+        <v>364421.6100000001</v>
       </c>
       <c r="E4" t="n">
-        <v>35567.62</v>
+        <v>33005.23</v>
       </c>
       <c r="F4" t="n">
-        <v>319541.4199999998</v>
+        <v>322842.9999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>82644.7800000001</v>
+        <v>74583.83999999991</v>
       </c>
       <c r="H4" t="n">
-        <v>1766.88</v>
+        <v>1775.41</v>
       </c>
       <c r="I4" t="n">
-        <v>217924.1699999999</v>
+        <v>229766.0999999999</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>627192.9399999998</v>
+        <v>710619.7</v>
       </c>
       <c r="C5" t="n">
-        <v>397426.84</v>
+        <v>403934.1700000001</v>
       </c>
       <c r="D5" t="n">
-        <v>364421.6099999999</v>
+        <v>381780.0999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>33005.23</v>
+        <v>22154.07</v>
       </c>
       <c r="F5" t="n">
-        <v>322842.9999999999</v>
+        <v>342959.6899999999</v>
       </c>
       <c r="G5" t="n">
-        <v>74583.83999999995</v>
+        <v>60974.48000000002</v>
       </c>
       <c r="H5" t="n">
-        <v>1775.41</v>
+        <v>1821.73</v>
       </c>
       <c r="I5" t="n">
-        <v>229766.0999999999</v>
+        <v>306685.5299999999</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>710619.6999999997</v>
+        <v>694497.6099999994</v>
       </c>
       <c r="C6" t="n">
-        <v>403934.1699999997</v>
+        <v>408306.8599999994</v>
       </c>
       <c r="D6" t="n">
-        <v>381780.0999999997</v>
+        <v>387163.6899999995</v>
       </c>
       <c r="E6" t="n">
-        <v>22154.07</v>
+        <v>21143.17</v>
       </c>
       <c r="F6" t="n">
-        <v>342959.6899999998</v>
+        <v>333512.7699999998</v>
       </c>
       <c r="G6" t="n">
-        <v>60974.48000000001</v>
+        <v>74794.09</v>
       </c>
       <c r="H6" t="n">
-        <v>1821.73</v>
+        <v>3234.910000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>306685.53</v>
+        <v>286190.75</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>694497.6099999996</v>
+        <v>617504.4599999997</v>
       </c>
       <c r="C7" t="n">
-        <v>408306.8599999996</v>
+        <v>386519.1599999997</v>
       </c>
       <c r="D7" t="n">
-        <v>387163.6899999996</v>
+        <v>365574.2899999997</v>
       </c>
       <c r="E7" t="n">
-        <v>21143.17</v>
+        <v>20944.87</v>
       </c>
       <c r="F7" t="n">
-        <v>333512.77</v>
+        <v>311200.3999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>74794.09000000003</v>
+        <v>75318.75999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3234.91</v>
+        <v>3228.19</v>
       </c>
       <c r="I7" t="n">
-        <v>286190.7500000001</v>
+        <v>230985.2999999999</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>617504.4599999998</v>
+        <v>622534.9400000004</v>
       </c>
       <c r="C8" t="n">
-        <v>386519.1599999999</v>
+        <v>402040.0700000004</v>
       </c>
       <c r="D8" t="n">
-        <v>365574.2899999998</v>
+        <v>374298.9400000004</v>
       </c>
       <c r="E8" t="n">
-        <v>20944.87</v>
+        <v>27741.13</v>
       </c>
       <c r="F8" t="n">
-        <v>311200.4</v>
+        <v>325000.92</v>
       </c>
       <c r="G8" t="n">
-        <v>75318.76000000004</v>
+        <v>77039.15000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>3228.19</v>
+        <v>3254.96</v>
       </c>
       <c r="I8" t="n">
-        <v>230985.3</v>
+        <v>220494.87</v>
       </c>
     </row>
     <row r="9">
@@ -694,28 +694,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>622534.9400000003</v>
+        <v>667821.5900000003</v>
       </c>
       <c r="C9" t="n">
-        <v>402040.0700000002</v>
+        <v>434753.1000000004</v>
       </c>
       <c r="D9" t="n">
-        <v>374298.9400000004</v>
+        <v>396669.5700000005</v>
       </c>
       <c r="E9" t="n">
-        <v>27741.13</v>
+        <v>38083.53000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>325000.9199999999</v>
+        <v>343613.1300000001</v>
       </c>
       <c r="G9" t="n">
-        <v>77039.15000000001</v>
+        <v>91139.96999999997</v>
       </c>
       <c r="H9" t="n">
-        <v>3254.96</v>
+        <v>3244.289999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>220494.87</v>
+        <v>233068.4899999999</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/concat_area_csm_qz.xlsx
+++ b/缓存数据/concat_area_csm_qz.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,18 +53,18 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -477,28 +477,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>605006.7800000001</v>
+        <v>1407787.59</v>
       </c>
       <c r="C2" t="n">
-        <v>410153.8900000001</v>
+        <v>730955.9200000003</v>
       </c>
       <c r="D2" t="n">
-        <v>387168.53</v>
+        <v>684848.41</v>
       </c>
       <c r="E2" t="n">
-        <v>22985.36</v>
+        <v>46107.50999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>333478.6900000001</v>
+        <v>330258.9299999998</v>
       </c>
       <c r="G2" t="n">
-        <v>76675.19999999997</v>
+        <v>400696.9899999996</v>
       </c>
       <c r="H2" t="n">
-        <v>1794.73</v>
+        <v>4472.679999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>194852.89</v>
+        <v>676831.6700000002</v>
       </c>
     </row>
     <row r="3">
@@ -508,28 +508,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>620110.3699999998</v>
+        <v>2775959.090000001</v>
       </c>
       <c r="C3" t="n">
-        <v>402186.1999999998</v>
+        <v>2055991.790000001</v>
       </c>
       <c r="D3" t="n">
-        <v>366618.5799999998</v>
+        <v>2013805.530000001</v>
       </c>
       <c r="E3" t="n">
-        <v>35567.62</v>
+        <v>42186.25999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>319541.4199999998</v>
+        <v>327641.53</v>
       </c>
       <c r="G3" t="n">
-        <v>82644.78000000004</v>
+        <v>1728350.26</v>
       </c>
       <c r="H3" t="n">
-        <v>1766.88</v>
+        <v>1604468.46</v>
       </c>
       <c r="I3" t="n">
-        <v>217924.17</v>
+        <v>719967.3</v>
       </c>
     </row>
     <row r="4">
@@ -539,28 +539,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>627192.9400000002</v>
+        <v>2835631.549999998</v>
       </c>
       <c r="C4" t="n">
-        <v>397426.8400000003</v>
+        <v>2146190.459999998</v>
       </c>
       <c r="D4" t="n">
-        <v>364421.6100000001</v>
+        <v>2106347.949999999</v>
       </c>
       <c r="E4" t="n">
-        <v>33005.23</v>
+        <v>39842.50999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>322842.9999999999</v>
+        <v>311887.3200000001</v>
       </c>
       <c r="G4" t="n">
-        <v>74583.83999999991</v>
+        <v>1834303.139999998</v>
       </c>
       <c r="H4" t="n">
-        <v>1775.41</v>
+        <v>1604475.45</v>
       </c>
       <c r="I4" t="n">
-        <v>229766.0999999999</v>
+        <v>689441.09</v>
       </c>
     </row>
     <row r="5">
@@ -570,28 +570,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>710619.7</v>
+        <v>2620673.690000001</v>
       </c>
       <c r="C5" t="n">
-        <v>403934.1700000001</v>
+        <v>2016719.440000002</v>
       </c>
       <c r="D5" t="n">
-        <v>381780.0999999999</v>
+        <v>1967348.260000002</v>
       </c>
       <c r="E5" t="n">
-        <v>22154.07</v>
+        <v>49371.17999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>342959.6899999999</v>
+        <v>328855.89</v>
       </c>
       <c r="G5" t="n">
-        <v>60974.48000000002</v>
+        <v>1687863.550000001</v>
       </c>
       <c r="H5" t="n">
-        <v>1821.73</v>
+        <v>1604445.28</v>
       </c>
       <c r="I5" t="n">
-        <v>306685.5299999999</v>
+        <v>603954.2499999998</v>
       </c>
     </row>
     <row r="6">
@@ -601,28 +601,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>694497.6099999994</v>
+        <v>2650322.090000001</v>
       </c>
       <c r="C6" t="n">
-        <v>408306.8599999994</v>
+        <v>2021408.87</v>
       </c>
       <c r="D6" t="n">
-        <v>387163.6899999995</v>
+        <v>1974115.33</v>
       </c>
       <c r="E6" t="n">
-        <v>21143.17</v>
+        <v>47293.53999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>333512.7699999998</v>
+        <v>346562.9199999999</v>
       </c>
       <c r="G6" t="n">
-        <v>74794.09</v>
+        <v>1674845.95</v>
       </c>
       <c r="H6" t="n">
-        <v>3234.910000000001</v>
+        <v>1604367.4</v>
       </c>
       <c r="I6" t="n">
-        <v>286190.75</v>
+        <v>628913.2200000004</v>
       </c>
     </row>
     <row r="7">
@@ -632,28 +632,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>617504.4599999997</v>
+        <v>1042274.890000001</v>
       </c>
       <c r="C7" t="n">
-        <v>386519.1599999997</v>
+        <v>396425.8100000001</v>
       </c>
       <c r="D7" t="n">
-        <v>365574.2899999997</v>
+        <v>358432.55</v>
       </c>
       <c r="E7" t="n">
-        <v>20944.87</v>
+        <v>37993.26</v>
       </c>
       <c r="F7" t="n">
-        <v>311200.3999999999</v>
+        <v>311888.3300000003</v>
       </c>
       <c r="G7" t="n">
-        <v>75318.75999999999</v>
+        <v>84537.47999999997</v>
       </c>
       <c r="H7" t="n">
-        <v>3228.19</v>
+        <v>5298.2</v>
       </c>
       <c r="I7" t="n">
-        <v>230985.2999999999</v>
+        <v>645849.0800000004</v>
       </c>
     </row>
     <row r="8">
@@ -663,28 +663,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>622534.9400000004</v>
+        <v>1051412.689999999</v>
       </c>
       <c r="C8" t="n">
-        <v>402040.0700000004</v>
+        <v>429940.7599999996</v>
       </c>
       <c r="D8" t="n">
-        <v>374298.9400000004</v>
+        <v>390746.4099999998</v>
       </c>
       <c r="E8" t="n">
-        <v>27741.13</v>
+        <v>39194.35</v>
       </c>
       <c r="F8" t="n">
-        <v>325000.92</v>
+        <v>311965.8899999998</v>
       </c>
       <c r="G8" t="n">
-        <v>77039.15000000001</v>
+        <v>117974.87</v>
       </c>
       <c r="H8" t="n">
-        <v>3254.96</v>
+        <v>5330.49</v>
       </c>
       <c r="I8" t="n">
-        <v>220494.87</v>
+        <v>621471.9299999999</v>
       </c>
     </row>
     <row r="9">
@@ -694,31 +694,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>667821.5900000003</v>
+        <v>960581.2699999993</v>
       </c>
       <c r="C9" t="n">
-        <v>434753.1000000004</v>
+        <v>469086.4799999998</v>
       </c>
       <c r="D9" t="n">
-        <v>396669.5700000005</v>
+        <v>425521.5799999999</v>
       </c>
       <c r="E9" t="n">
-        <v>38083.53000000001</v>
+        <v>43564.89999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>343613.1300000001</v>
+        <v>320884.3899999999</v>
       </c>
       <c r="G9" t="n">
-        <v>91139.96999999997</v>
+        <v>148202.09</v>
       </c>
       <c r="H9" t="n">
-        <v>3244.289999999999</v>
+        <v>5279.33</v>
       </c>
       <c r="I9" t="n">
-        <v>233068.4899999999</v>
+        <v>491494.7899999996</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>